--- a/data/raw_lab_data/Fuhrberg CHNS.xlsx
+++ b/data/raw_lab_data/Fuhrberg CHNS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vcantarella/Documents/FFA_colexperiment/data/raw_lab_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vcant\Documents\ffa_colexperiment\data\raw_lab_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4B69E2-B4BD-E047-A6F8-40ABAA0D74C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3CF501-B963-401A-BA0E-B49B7A93889E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="740" windowWidth="28260" windowHeight="16680" xr2:uid="{D8F29EDB-924B-AB45-BE47-83C51CA64082}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8F29EDB-924B-AB45-BE47-83C51CA64082}"/>
   </bookViews>
   <sheets>
     <sheet name="260212_Johann_KS" sheetId="1" r:id="rId1"/>
@@ -235,6 +235,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -988,14 +989,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8772BC25-4518-9842-9E69-834456E81B64}">
   <dimension ref="B1:U37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:21" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1021,7 +1022,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:21" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3">
         <v>10.823</v>
       </c>
@@ -1046,7 +1047,7 @@
       <c r="I2" s="3"/>
       <c r="U2" s="1"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>151.66200000000001</v>
       </c>
@@ -1073,7 +1074,7 @@
       </c>
       <c r="U3" s="1"/>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>137.50700000000001</v>
       </c>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>135.72</v>
       </c>
@@ -1127,7 +1128,7 @@
       </c>
       <c r="U5" s="1"/>
     </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>136.49799999999999</v>
       </c>
@@ -1154,7 +1155,7 @@
       </c>
       <c r="U6" s="1"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>150.47</v>
       </c>
@@ -1181,7 +1182,7 @@
       </c>
       <c r="U7" s="1"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>140.30199999999999</v>
       </c>
@@ -1208,7 +1209,7 @@
       </c>
       <c r="U8" s="1"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>142.80199999999999</v>
       </c>
@@ -1235,7 +1236,7 @@
       </c>
       <c r="U9" s="1"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>127.255</v>
       </c>
@@ -1262,7 +1263,7 @@
       </c>
       <c r="U10" s="1"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>129.47800000000001</v>
       </c>
@@ -1289,7 +1290,7 @@
       </c>
       <c r="U11" s="1"/>
     </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>143.023</v>
       </c>
@@ -1316,7 +1317,7 @@
       </c>
       <c r="U12" s="1"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>140.22</v>
       </c>
@@ -1343,7 +1344,7 @@
       </c>
       <c r="U13" s="1"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <v>139.39599999999999</v>
       </c>
@@ -1370,7 +1371,7 @@
       </c>
       <c r="U14" s="1"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>135.74299999999999</v>
       </c>
@@ -1397,7 +1398,7 @@
       </c>
       <c r="U15" s="1"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <v>140.953</v>
       </c>
@@ -1424,7 +1425,7 @@
       </c>
       <c r="U16" s="1"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <v>137.27000000000001</v>
       </c>
@@ -1451,7 +1452,7 @@
       </c>
       <c r="U17" s="1"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="3">
         <v>130.26300000000001</v>
       </c>
@@ -1478,7 +1479,7 @@
       </c>
       <c r="U18" s="1"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
         <v>136.952</v>
       </c>
@@ -1505,7 +1506,7 @@
       </c>
       <c r="U19" s="1"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <v>132.19200000000001</v>
       </c>
@@ -1532,7 +1533,7 @@
       </c>
       <c r="U20" s="1"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
         <v>134.26300000000001</v>
       </c>
@@ -1559,7 +1560,7 @@
       </c>
       <c r="U21" s="1"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <v>140.17400000000001</v>
       </c>
@@ -1586,7 +1587,7 @@
       </c>
       <c r="U22" s="1"/>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
         <v>61.639000000000003</v>
       </c>
@@ -1613,7 +1614,7 @@
       </c>
       <c r="U23" s="1"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="3">
         <v>62.476999999999997</v>
       </c>
@@ -1640,7 +1641,7 @@
       </c>
       <c r="U24" s="1"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
         <v>60.802</v>
       </c>
@@ -1667,7 +1668,7 @@
       </c>
       <c r="U25" s="1"/>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="3">
         <v>63.991999999999997</v>
       </c>
@@ -1694,37 +1695,37 @@
       </c>
       <c r="U26" s="1"/>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U27" s="1"/>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U28" s="1"/>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U29" s="1"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U30" s="1"/>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U31" s="1"/>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="U32" s="1"/>
     </row>
-    <row r="33" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U33" s="1"/>
     </row>
-    <row r="34" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U34" s="1"/>
     </row>
-    <row r="35" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U35" s="1"/>
     </row>
-    <row r="36" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U36" s="1"/>
     </row>
-    <row r="37" spans="21:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U37" s="1"/>
     </row>
   </sheetData>
